--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A13"/>
+  <dimension ref="A2:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -501,12 +501,103 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>CWcwKOO8</t>
         </is>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A26"/>
+  <dimension ref="A2:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -515,89 +515,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WhAFMMRi</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>CWcwKOO8</t>
         </is>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A15"/>
+  <dimension ref="A2:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -515,12 +515,61 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>CWcwKOO8</t>
         </is>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,155 +425,593 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A22"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
-        </is>
-      </c>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bygTWQzR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>anuar</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SChm1pCo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>exposito edu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KxSmFSum</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>alfonso pedraza</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OQY4TKul</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>marcos paulo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>vcqiFPHQ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>foyth juan</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>xWwucZ71</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>suarez denis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
-        </is>
-      </c>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
-        </is>
-      </c>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
-        </is>
-      </c>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
-        </is>
-      </c>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
-        </is>
-      </c>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
-        </is>
-      </c>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
-        </is>
-      </c>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
-        </is>
-      </c>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
-        </is>
-      </c>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
-        </is>
-      </c>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
-        </is>
-      </c>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
-        </is>
-      </c>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,151 +425,221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A22"/>
+  <dimension ref="A2:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>OlferefS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>CWcwKOO8</t>
         </is>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,177 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A32"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>8KIT2SzJ</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GW5JRBD0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>de la torre luca</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Au7zDEEL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>guaita vicente</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2iri9TaP</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>canos sergi</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>O6bdhMA2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>castillejo samu</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2gqO56Xu</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>diakhaby mouctar</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>KbobTIgr</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>domenech jaume</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>xWguLPCU</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>gaya jose</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>bePNNa1r</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>perez francisco</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +603,62 @@
           <t>QekfJmLa</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fefkCPrH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>lokonga sambi</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Aexbrioc</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>suso</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KxSmFSum</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>alfonso pedraza</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vcqiFPHQ</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>foyth juan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>xWwucZ71</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>suarez denis</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +666,22 @@
           <t>vJDNK0d4</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +689,22 @@
           <t>WhAFMMRi</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +712,22 @@
           <t>OQqSjnv9</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +735,22 @@
           <t>YcAFQVSP</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +758,22 @@
           <t>IVonL9jm</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +781,22 @@
           <t>hA5zaJZp</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +804,22 @@
           <t>MNr3HRkC</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +827,22 @@
           <t>ChPK4l66</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -504,6 +850,22 @@
           <t>hpMqQeYq</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -511,6 +873,22 @@
           <t>4KmdZaBc</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -518,6 +896,22 @@
           <t>8CpDVHAM</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -525,6 +919,22 @@
           <t>0Y1WIvRG</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -532,6 +942,22 @@
           <t>f92vnwe3</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -539,6 +965,22 @@
           <t>KhwykQ8L</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -546,6 +988,22 @@
           <t>v1KiOZ2d</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -553,6 +1011,22 @@
           <t>CQ0ABdJj</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -560,6 +1034,22 @@
           <t>0ns5XwtA</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -567,6 +1057,22 @@
           <t>OlferefS</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -574,6 +1080,22 @@
           <t>SM0npHPF</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -581,6 +1103,22 @@
           <t>GOO6q4Wr</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -588,6 +1126,22 @@
           <t>xhKUdf9L</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -595,6 +1149,22 @@
           <t>EJYZzDn2</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -602,6 +1172,22 @@
           <t>tQQLbGv9</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -609,6 +1195,22 @@
           <t>vyy1kC1e</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -616,6 +1218,22 @@
           <t>n1v9mjW7</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -623,6 +1241,22 @@
           <t>h4pRxZHk</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -630,20 +1264,22 @@
           <t>YN50iYWr</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,40 +461,60 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
@@ -503,190 +523,793 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8psoD6vm</t>
+          <t>hKx3nCTp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>arnaiz jose</t>
+          <t>alaba david</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KxtC5I27</t>
+          <t>QNvlPm7s</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>barja enrique</t>
+          <t>bellingham jude</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>hvSbhBpg</t>
+          <t>6ekYsPfO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pena ruben</t>
+          <t>camavinga eduardo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ew10Xoy6</t>
+          <t>KnytnSKl</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>llabres javier</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>mendy ferland</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>WSRdoQ7I</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vallejo jesus</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>bygTWQzR</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>anuar</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>A1F3rz9c</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>de jong frenkie</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>xrV9v8CU</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>gavi</t>
-        </is>
-      </c>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ChK2eOCj</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>paredes aitor</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>AqAnv17H</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>inigo ruiz</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>nPdiENxr</t>
+          <t>6qyeYCYO</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>serrano nico</t>
+          <t>januzaj adnan</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Ao9Vw3hi</t>
+          <t>St8XPCaD</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>simon unai</t>
-        </is>
-      </c>
+          <t>pejino</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SChm1pCo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>exposito edu</t>
-        </is>
-      </c>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>r7qw7OKg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>zakharian arsen</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>vZ3QJXBc</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bakambu cedric</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>f7TcxoGd</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>garreta felix marti</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ULLmpdEb</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>isco</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>by4YfNNK</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>mendy nobel</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OQY4TKul</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>marcos paulo</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SdatvAiU</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>mendez diego</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>vDI9I1M4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>artero ricard</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>tGPWeqJs</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>vcqiFPHQ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>foyth juan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>xWwucZ71</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>suarez denis</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ew10Xoy6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>llabres javier</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>jRBXx0H4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>morey mateu</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>nmjvsTy0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>jordan joan</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Aexbrioc</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>suso</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SdatvAiU</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mendez diego</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Eo8SAMoI</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ratiu andrei</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ShxiZhJI</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>christensen andreas</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>A1F3rz9c</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>de jong frenkie</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>dUPVnxzP</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>fati ansu</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>xrV9v8CU</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>gavi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,321 +451,405 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hKx3nCTp</t>
+          <t>vcqiFPHQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alaba david</t>
+          <t>foyth juan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QNvlPm7s</t>
+          <t>xWwucZ71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>bellingham jude</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>6ekYsPfO</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>camavinga eduardo</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>KnytnSKl</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>mendy ferland</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>WSRdoQ7I</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vallejo jesus</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>bygTWQzR</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>anuar</t>
-        </is>
-      </c>
+          <t>suarez denis</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ew10Xoy6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>llabres javier</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jRBXx0H4</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>morey mateu</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Aexbrioc</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>suso</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>6qyeYCYO</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>januzaj adnan</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>St8XPCaD</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>pejino</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SdatvAiU</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mendez diego</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Eo8SAMoI</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ratiu andrei</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ShxiZhJI</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>christensen andreas</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>A1F3rz9c</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>de jong frenkie</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dUPVnxzP</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fati ansu</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>vZ3QJXBc</t>
+          <t>xrV9v8CU</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bakambu cedric</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>f7TcxoGd</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>garreta felix marti</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>ULLmpdEb</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>isco</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>by4YfNNK</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>mendy nobel</t>
-        </is>
-      </c>
+          <t>gavi</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OQY4TKul</t>
+          <t>hxVl8TRJ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>marcos paulo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>djalo alvaro</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ChK2eOCj</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>paredes aitor</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2iri9TaP</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>canos sergi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O6bdhMA2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>castillejo samu</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2gqO56Xu</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>diakhaby mouctar</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>vDI9I1M4</t>
+          <t>KbobTIgr</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>artero ricard</t>
+          <t>domenech jaume</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>tGPWeqJs</t>
+          <t>AqAnv17H</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>jastin antonino</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>inigo ruiz</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>nPdiENxr</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>serrano nico</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Ao9Vw3hi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>simon unai</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>xWguLPCU</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>gaya jose</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>bePNNa1r</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>perez francisco</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vcqiFPHQ</t>
+          <t>bygTWQzR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>foyth juan</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>xWwucZ71</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>suarez denis</t>
-        </is>
-      </c>
+          <t>anuar</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -780,141 +864,137 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ew10Xoy6</t>
+          <t>jX8PENMO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>llabres javier</t>
+          <t>lemar thomas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>jRBXx0H4</t>
+          <t>OQY4TKul</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>morey mateu</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>marcos paulo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SChm1pCo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>exposito edu</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>nmjvsTy0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>jordan joan</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Aexbrioc</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>suso</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SdatvAiU</t>
+          <t>A3vo4Lf6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mendez diego</t>
+          <t>barrenetxea muguruza ander</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Eo8SAMoI</t>
+          <t>0zO9SfkA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ratiu andrei</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>odriozola alvaro</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>h4BWTxSF</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>sedlar aleksandar</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ShxiZhJI</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>christensen andreas</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>A1F3rz9c</t>
+          <t>r7qw7OKg</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>de jong frenkie</t>
+          <t>zakharian arsen</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>dUPVnxzP</t>
+          <t>phTjGNq0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>fati ansu</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>xrV9v8CU</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>gavi</t>
-        </is>
-      </c>
+          <t>zubeldia igor</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -935,11 +1015,15 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -960,11 +1044,15 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -985,11 +1073,15 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1010,11 +1102,15 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1035,11 +1131,15 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1060,11 +1160,15 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1085,11 +1189,15 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1110,11 +1218,15 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1135,11 +1247,15 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1160,11 +1276,15 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1185,11 +1305,15 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1210,106 +1334,10 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,176 +451,152 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>vcqiFPHQ</t>
+          <t>ChK2eOCj</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>foyth juan</t>
+          <t>paredes aitor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>xWwucZ71</t>
+          <t>AqAnv17H</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>suarez denis</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+          <t>inigo ruiz</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ao9Vw3hi</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>simon unai</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>O6bdhMA2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>castillejo samu</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2gqO56Xu</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>diakhaby mouctar</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>KbobTIgr</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>domenech jaume</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>xWguLPCU</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>gaya jose</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ew10Xoy6</t>
+          <t>bygTWQzR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>llabres javier</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>jRBXx0H4</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>morey mateu</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Aexbrioc</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>suso</t>
-        </is>
-      </c>
+          <t>anuar</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -629,372 +605,220 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SdatvAiU</t>
+          <t>OQY4TKul</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mendez diego</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Eo8SAMoI</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ratiu andrei</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ShxiZhJI</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>christensen andreas</t>
-        </is>
-      </c>
+          <t>marcos paulo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>A1F3rz9c</t>
+          <t>SChm1pCo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>de jong frenkie</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dUPVnxzP</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fati ansu</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>xrV9v8CU</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gavi</t>
-        </is>
-      </c>
+          <t>exposito edu</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hxVl8TRJ</t>
+          <t>r7qw7OKg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>djalo alvaro</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ChK2eOCj</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>paredes aitor</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2iri9TaP</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>canos sergi</t>
-        </is>
-      </c>
+          <t>zakharian arsen</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>O6bdhMA2</t>
+          <t>h4BWTxSF</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>castillejo samu</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2gqO56Xu</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>diakhaby mouctar</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>KbobTIgr</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>domenech jaume</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>AqAnv17H</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>inigo ruiz</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>nPdiENxr</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>serrano nico</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Ao9Vw3hi</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>simon unai</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>xWguLPCU</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>gaya jose</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>bePNNa1r</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>perez francisco</t>
-        </is>
-      </c>
+          <t>sedlar aleksandar</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bygTWQzR</t>
+          <t>vDI9I1M4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>anuar</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>artero ricard</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>tGPWeqJs</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>jastin antonino</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>KxtC5I27</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>barja enrique</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ncU1c1uo</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>munoz iker</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jX8PENMO</t>
+          <t>6qyeYCYO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lemar thomas</t>
+          <t>januzaj adnan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OQY4TKul</t>
+          <t>St8XPCaD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>marcos paulo</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SChm1pCo</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>exposito edu</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>pejino</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>hKx3nCTp</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>alaba david</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>QNvlPm7s</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>bellingham jude</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6ekYsPfO</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>camavinga eduardo</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>A3vo4Lf6</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>barrenetxea muguruza ander</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0zO9SfkA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>odriozola alvaro</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>h4BWTxSF</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>sedlar aleksandar</t>
-        </is>
-      </c>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>r7qw7OKg</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>zakharian arsen</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>phTjGNq0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>zubeldia igor</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -1011,19 +835,11 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -1040,19 +856,11 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1069,19 +877,11 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1098,19 +898,11 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1127,19 +919,11 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1156,19 +940,11 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1185,19 +961,11 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1214,19 +982,11 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1243,101 +1003,6 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,140 +461,212 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ChK2eOCj</t>
+          <t>M3sbJix9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>paredes aitor</t>
+          <t>araujo ronald</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AqAnv17H</t>
+          <t>bmlJ8bjQ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>inigo ruiz</t>
+          <t>barbera victor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ao9Vw3hi</t>
+          <t>pf3IOiFD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>simon unai</t>
+          <t>bernal marc</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>O6bdhMA2</t>
+          <t>ShxiZhJI</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>castillejo samu</t>
+          <t>christensen andreas</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2gqO56Xu</t>
+          <t>A1F3rz9c</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>diakhaby mouctar</t>
+          <t>de jong frenkie</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>KbobTIgr</t>
+          <t>dUPVnxzP</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>domenech jaume</t>
+          <t>fati ansu</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>xWguLPCU</t>
+          <t>AyxD3I5C</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>gaya jose</t>
-        </is>
-      </c>
+          <t>garcia eric</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>xrV9v8CU</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>gavi</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bygTWQzR</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>anuar</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bygTWQzR</t>
+          <t>AqAnv17H</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>anuar</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>inigo ruiz</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ao9Vw3hi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>simon unai</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -605,205 +677,253 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OQY4TKul</t>
+          <t>IsOwrMdM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>marcos paulo</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>cabrera leandro</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SChm1pCo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>exposito edu</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SChm1pCo</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>exposito edu</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>SdatvAiU</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>mendez diego</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>r7qw7OKg</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>zakharian arsen</t>
-        </is>
-      </c>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>h4BWTxSF</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>sedlar aleksandar</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Ew10Xoy6</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>llabres javier</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>jRBXx0H4</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>morey mateu</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vDI9I1M4</t>
+          <t>2gqO56Xu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>artero ricard</t>
+          <t>diakhaby mouctar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>tGPWeqJs</t>
+          <t>KbobTIgr</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>jastin antonino</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>KxtC5I27</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>barja enrique</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ncU1c1uo</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>munoz iker</t>
-        </is>
-      </c>
+          <t>domenech jaume</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>xWguLPCU</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>gaya jose</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>vcqiFPHQ</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>foyth juan</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>xWwucZ71</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>suarez denis</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6qyeYCYO</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>januzaj adnan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>St8XPCaD</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>pejino</t>
-        </is>
-      </c>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>hKx3nCTp</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>alaba david</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>QNvlPm7s</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>bellingham jude</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>6ekYsPfO</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>camavinga eduardo</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>6qyeYCYO</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>januzaj adnan</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>St8XPCaD</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>pejino</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KxtC5I27</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>barja enrique</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ncU1c1uo</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>munoz iker</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -814,17 +934,49 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>8zW214va</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ristic mihailo</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hSbvVwW7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>niguez saul</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Aexbrioc</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>suso</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -835,11 +987,35 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>vDI9I1M4</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>artero ricard</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>tGPWeqJs</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -856,19 +1032,67 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>dQ1P695O</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>oyarzabal mikel</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>r7qw7OKg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>zakharian arsen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>hKx3nCTp</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>alaba david</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>QNvlPm7s</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>bellingham jude</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6ekYsPfO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>camavinga eduardo</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -877,132 +1101,38 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>vZ3QJXBc</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>bakambu cedric</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>f7TcxoGd</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>garreta felix marti</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>by4YfNNK</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>mendy nobel</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,359 +425,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A2:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>6qyeYCYO</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>januzaj adnan</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>St8XPCaD</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>pejino</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>YeqTho8m</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>tY4UH3ql</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>allende tadeo</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>v1XgteJr</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>cervi franco</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>KxtC5I27</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>barja enrique</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ncU1c1uo</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>munoz iker</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GW5JRBD0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>de la torre luca</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>8zW214va</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ristic mihailo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>08zpk37C</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>vDI9I1M4</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>artero ricard</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>tGPWeqJs</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>jastin antonino</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>hSbvVwW7</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>niguez saul</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2s2ATpKI</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ocampos lucas</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Aexbrioc</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>suso</t>
+          <t>CjIFsr1e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>dQ1P695O</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>oyarzabal mikel</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>r7qw7OKg</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>zakharian arsen</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>QXjmYRUE</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>rodriguez alvaro</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>8EcB5Oig</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>vZ3QJXBc</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>bakambu cedric</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>f7TcxoGd</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>garreta felix marti</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>hKx3nCTp</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>alaba david</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>QNvlPm7s</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>bellingham jude</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>by4YfNNK</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mendy nobel</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>6ekYsPfO</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>camavinga eduardo</t>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A11"/>
+  <dimension ref="A2:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -498,6 +498,118 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,190 +425,606 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A27"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YeqTho8m</t>
-        </is>
-      </c>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GW5JRBD0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>de la torre luca</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>f79qYNc4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>dominguez carlos</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>IXim7pWh</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>gonzalez alfonso</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8bvxeNAG</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>manquillo javier</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8zW214va</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ristic mihailo</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>bygTWQzR</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>anuar</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>AJg8NPiE</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ruiz raul chasco</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>6NytetE5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>sanchez javier</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>08zpk37C</t>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>vDI9I1M4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>artero ricard</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tGPWeqJs</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>M3sbJix9</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>araujo ronald</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>pf3IOiFD</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>bernal marc</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ShxiZhJI</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>christensen andreas</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>A1F3rz9c</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>de jong frenkie</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>xrV9v8CU</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>gavi</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2c2ipETG</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>marin fermin</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CjIFsr1e</t>
-        </is>
-      </c>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>nev6Da3D</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>alvarez yeray</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>AqAnv17H</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>inigo ruiz</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ao9Vw3hi</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>simon unai</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8EcB5Oig</t>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AaZiGJ9E</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>barrios pablo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>jX8PENMO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lemar thomas</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2gqO56Xu</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>diakhaby mouctar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>KbobTIgr</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>domenech jaume</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>EP4vWYSf</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>duro hugo</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>xWguLPCU</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>gaya jose</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>IXRaCzVt</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>mir rafael</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>bePNNa1r</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>perez francisco</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jckS1tiI</t>
-        </is>
-      </c>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>vHFG4hw9</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>espino alfonso</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SdatvAiU</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mendez diego</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>KxtC5I27</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>barja enrique</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ncU1c1uo</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>munoz iker</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>na927pNt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>dzUhmsxP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SdHeBgOE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>fVeJ32M5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
           <t>AyPaTn1c</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>8b5vHIeT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xjut9IFr</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IRBb0lXA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYbQEmn4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4b2YCRGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>xWrPG9Hi</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ImLNuMV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>dCNk2A2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>OAmz0KLU</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pxdwg6Pp</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>QiF6bS1N</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>445r4WXo</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rkN7RQV9</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>bwZsTw7E</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>f5SjRHyR</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hCPqc747</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>lato toni</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ew10Xoy6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>llabres javier</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KvHXl88g</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>maffeo pablo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>jRBXx0H4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>morey mateu</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fToJY0qQ</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>van der heyden siebe</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Ey5XjmJt</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>mendez brais</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>fRSnvKQG</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>traore hamari</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>r7qw7OKg</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>zakharian arsen</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,560 +471,997 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GW5JRBD0</t>
+          <t>hCPqc747</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>de la torre luca</t>
+          <t>lato toni</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>f79qYNc4</t>
+          <t>Ew10Xoy6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>dominguez carlos</t>
+          <t>llabres javier</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IXim7pWh</t>
+          <t>KvHXl88g</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>gonzalez alfonso</t>
+          <t>maffeo pablo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8bvxeNAG</t>
+          <t>fToJY0qQ</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>manquillo javier</t>
+          <t>van der heyden siebe</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8zW214va</t>
+          <t>MaufHIJ2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ristic mihailo</t>
+          <t>lopez javi</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>bygTWQzR</t>
+          <t>Ey5XjmJt</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>anuar</t>
+          <t>mendez brais</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>AJg8NPiE</t>
+          <t>fRSnvKQG</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ruiz raul chasco</t>
+          <t>traore hamari</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6NytetE5</t>
+          <t>r7qw7OKg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>sanchez javier</t>
+          <t>zakharian arsen</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>8b5vHIeT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vDI9I1M4</t>
+          <t>vZ3QJXBc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>artero ricard</t>
+          <t>bakambu cedric</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tGPWeqJs</t>
+          <t>8K4WA9Gh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>jastin antonino</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>bartra marc</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>jmbMzvQa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>carvalho william</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ULLmpdEb</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>isco</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>lWTa55Ta</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nabil aberdin</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>M3sbJix9</t>
+          <t>fLceoUtl</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>araujo ronald</t>
+          <t>alderete omar</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>pf3IOiFD</t>
+          <t>8OTCRUh0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>bernal marc</t>
+          <t>mayoral borja</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ShxiZhJI</t>
+          <t>QXjmYRUE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>christensen andreas</t>
+          <t>rodriguez alvaro</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>A1F3rz9c</t>
+          <t>0vLnUdTa</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>de jong frenkie</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>xrV9v8CU</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>gavi</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2c2ipETG</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>marin fermin</t>
+          <t>juanmi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fwWfEJpk</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>garcia naim</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>nev6Da3D</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>alvarez yeray</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>nev6Da3D</t>
+          <t>hOdEyz15</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>alvarez yeray</t>
+          <t>jauregizar mikel</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>AqAnv17H</t>
+          <t>Ao9Vw3hi</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>inigo ruiz</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ao9Vw3hi</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
           <t>simon unai</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AaZiGJ9E</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>barrios pablo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>jX8PENMO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>lemar thomas</t>
-        </is>
-      </c>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2gqO56Xu</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>diakhaby mouctar</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>KbobTIgr</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>domenech jaume</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>EP4vWYSf</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>duro hugo</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>xWguLPCU</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>gaya jose</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>IXRaCzVt</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>mir rafael</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>bePNNa1r</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>perez francisco</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>vHFG4hw9</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>espino alfonso</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SdatvAiU</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>mendez diego</t>
-        </is>
-      </c>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>KxtC5I27</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>barja enrique</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>ncU1c1uo</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>munoz iker</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>hCPqc747</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>lato toni</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ew10Xoy6</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>llabres javier</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>KvHXl88g</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>maffeo pablo</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>jRBXx0H4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>morey mateu</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fToJY0qQ</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>van der heyden siebe</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Ey5XjmJt</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>mendez brais</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>fRSnvKQG</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>traore hamari</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>r7qw7OKg</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>zakharian arsen</t>
-        </is>
-      </c>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,142 +521,162 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_5</t>
+          <t>id_player_miss_home_6</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_5</t>
+          <t>player_name_miss_home_6</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_6</t>
+          <t>id_player_miss_home_7</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_6</t>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GW5JRBD0</t>
+          <t>8K4WA9Gh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>de la torre luca</t>
+          <t>bartra marc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>f79qYNc4</t>
+          <t>jmbMzvQa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>dominguez carlos</t>
+          <t>carvalho william</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IXim7pWh</t>
+          <t>ULLmpdEb</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>gonzalez alfonso</t>
+          <t>isco</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8bvxeNAG</t>
+          <t>v5Xtt1xa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>manquillo javier</t>
+          <t>johnny cardoso</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8zW214va</t>
+          <t>vFNb1rQ5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ristic mihailo</t>
+          <t>sabaly youssouf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>bygTWQzR</t>
+          <t>lrscbe6I</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>anuar</t>
+          <t>asano takuma</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>AJg8NPiE</t>
+          <t>Ew10Xoy6</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ruiz raul chasco</t>
+          <t>llabres javier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6NytetE5</t>
+          <t>CjwNDgqi</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>sanchez javier</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>muriqi vedat</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>fToJY0qQ</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>van der heyden siebe</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vDI9I1M4</t>
+          <t>fefkCPrH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>artero ricard</t>
+          <t>lokonga sambi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tGPWeqJs</t>
+          <t>tUNr1qOE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>jastin antonino</t>
+          <t>sow djibril</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -667,235 +687,209 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>M3sbJix9</t>
+          <t>bygTWQzR</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>araujo ronald</t>
+          <t>anuar</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>pf3IOiFD</t>
+          <t>6NytetE5</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>bernal marc</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>ShxiZhJI</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>christensen andreas</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>A1F3rz9c</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>de jong frenkie</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>xrV9v8CU</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>gavi</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2c2ipETG</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>marin fermin</t>
-        </is>
-      </c>
+          <t>sanchez javier</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2gqO56Xu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>diakhaby mouctar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KbobTIgr</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>domenech jaume</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EP4vWYSf</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>duro hugo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>xWguLPCU</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>gaya jose</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>IXRaCzVt</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>mir rafael</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>nev6Da3D</t>
+          <t>ncU1c1uo</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>alvarez yeray</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>AqAnv17H</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>inigo ruiz</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ao9Vw3hi</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>simon unai</t>
-        </is>
-      </c>
+          <t>munoz iker</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>bePNNa1r</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>perez francisco</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AaZiGJ9E</t>
+          <t>hKx3nCTp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>barrios pablo</t>
+          <t>alaba david</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>jX8PENMO</t>
+          <t>6ekYsPfO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>lemar thomas</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>camavinga eduardo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>zPYmze7F</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ceballos dani</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nm2Qvnyk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>diaz brahim</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2gqO56Xu</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>diakhaby mouctar</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>KbobTIgr</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>domenech jaume</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>EP4vWYSf</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>duro hugo</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>xWguLPCU</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>gaya jose</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>IXRaCzVt</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>mir rafael</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>bePNNa1r</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>perez francisco</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>vHFG4hw9</t>
+          <t>vDI9I1M4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>espino alfonso</t>
+          <t>artero ricard</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SdatvAiU</t>
+          <t>tGPWeqJs</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>mendez diego</t>
+          <t>jastin antonino</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -906,22 +900,22 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>KxtC5I27</t>
+          <t>vHFG4hw9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>barja enrique</t>
+          <t>espino alfonso</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ncU1c1uo</t>
+          <t>SdatvAiU</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>munoz iker</t>
+          <t>mendez diego</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -932,99 +926,816 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hCPqc747</t>
+          <t>M3sbJix9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lato toni</t>
+          <t>araujo ronald</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ew10Xoy6</t>
+          <t>pf3IOiFD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>llabres javier</t>
+          <t>bernal marc</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KvHXl88g</t>
+          <t>ShxiZhJI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>maffeo pablo</t>
+          <t>christensen andreas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>jRBXx0H4</t>
+          <t>A1F3rz9c</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>morey mateu</t>
+          <t>de jong frenkie</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fToJY0qQ</t>
+          <t>xrV9v8CU</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>van der heyden siebe</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Ey5XjmJt</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>mendez brais</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>fRSnvKQG</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>traore hamari</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>r7qw7OKg</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>zakharian arsen</t>
-        </is>
-      </c>
+          <t>gavi</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2c2ipETG</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>marin fermin</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2oVBOlPg</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>olmo dani</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>byxc46yl</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>ter stegen marc andre</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,267 +461,281 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_7</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_7</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_8</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_8</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bygTWQzR</t>
+          <t>n9uHpbM8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>anuar</t>
+          <t>bamba jonathan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0n8qUmN8</t>
+          <t>GW5JRBD0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>de la hoz cesar</t>
+          <t>de la torre luca</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Iefc5Fwo</t>
+          <t>8zW214va</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ozkacar cenk</t>
+          <t>ristic mihailo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6NytetE5</t>
+          <t>vDI9I1M4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>sanchez javier</t>
+          <t>artero ricard</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>lrscbe6I</t>
+          <t>tGPWeqJs</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>asano takuma</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Ew10Xoy6</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>llabres javier</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>CjwNDgqi</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>muriqi vedat</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>pbb8dhGG</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>valjent martin</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>fToJY0qQ</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>van der heyden siebe</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nev6Da3D</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>alvarez yeray</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jyzWX8yk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>herrera ander</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>t2Srcdis</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>prados benat</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>OOFwBfsT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>marcao</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>hSbvVwW7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>niguez saul</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hpZLKZVC</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>sancet ohian</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ao9Vw3hi</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>simon unai</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>OK0Lcg44</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>romero isaac</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>tUNr1qOE</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>sow djibril</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vHFG4hw9</t>
+          <t>jmbMzvQa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>espino alfonso</t>
+          <t>carvalho william</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SdatvAiU</t>
+          <t>ULLmpdEb</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>mendez diego</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>isco</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>vFNb1rQ5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>sabaly youssouf</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>IsOwrMdM</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cabrera leandro</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SbettZSO</t>
+          <t>SChm1pCo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>neyou noupa yvan</t>
+          <t>exposito edu</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -732,462 +746,152 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fRSnvKQG</t>
+          <t>CMGUADgt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>traore hamari</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>r7qw7OKg</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>zakharian arsen</t>
-        </is>
-      </c>
+          <t>azpilicueta cesar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>zPYmze7F</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ceballos dani</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2gqO56Xu</t>
+          <t>nm2Qvnyk</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>diakhaby mouctar</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>KbobTIgr</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>domenech jaume</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>xWguLPCU</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>gaya jose</t>
-        </is>
-      </c>
+          <t>diaz brahim</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>IXRaCzVt</t>
+          <t>Wn6E2SED</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>mir rafael</t>
+          <t>mbappe kylian</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ncU1c1uo</t>
+          <t>KxSmFSum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>munoz iker</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>alfonso pedraza</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>vcqiFPHQ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>foyth juan</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>S6QWzDng</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>kambwala willy</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Cz3awDFR</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>marmol mika</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>M3sbJix9</t>
+          <t>AerDGNDO</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>araujo ronald</t>
+          <t>mckenna scott</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>pf3IOiFD</t>
+          <t>UwfDD083</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>bernal marc</t>
+          <t>moreno gerard</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ShxiZhJI</t>
+          <t>8fnHDvMe</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>christensen andreas</t>
+          <t>santos yeremi</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A1F3rz9c</t>
+          <t>SjTBQO7b</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>de jong frenkie</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>xrV9v8CU</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>gavi</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2c2ipETG</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>marin fermin</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2oVBOlPg</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>olmo dani</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>byxc46yl</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>ter stegen marc andre</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>GW5JRBD0</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>de la torre luca</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>YkHSwt2b</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>mingueza oscar</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>vDI9I1M4</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>artero ricard</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>tGPWeqJs</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>jastin antonino</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>nev6Da3D</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>alvarez yeray</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Ao9Vw3hi</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>simon unai</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>OOFwBfsT</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>marcao</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hSbvVwW7</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>niguez saul</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>tUNr1qOE</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>sow djibril</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>jmbMzvQa</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>carvalho william</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ULLmpdEb</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>isco</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>vFNb1rQ5</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>sabaly youssouf</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>SChm1pCo</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>exposito edu</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CMGUADgt</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>azpilicueta cesar</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>hKx3nCTp</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>alaba david</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>zPYmze7F</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ceballos dani</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>nm2Qvnyk</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>diaz brahim</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Wn6E2SED</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>mbappe kylian</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+          <t>park marvin</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,303 +441,297 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_5</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_5</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>QmPfsURO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>n9uHpbM8</t>
+          <t>fwWfEJpk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bamba jonathan</t>
+          <t>garcia naim</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GW5JRBD0</t>
+          <t>2gqO56Xu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>de la torre luca</t>
+          <t>diakhaby mouctar</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8zW214va</t>
+          <t>KbobTIgr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ristic mihailo</t>
+          <t>domenech jaume</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>vDI9I1M4</t>
+          <t>xWguLPCU</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>artero ricard</t>
+          <t>gaya jose</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>tGPWeqJs</t>
+          <t>IXRaCzVt</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>jastin antonino</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>mir rafael</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>M5U2cN2q</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vazquez jesus</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>0AJjqex0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nev6Da3D</t>
+          <t>IsOwrMdM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>alvarez yeray</t>
+          <t>cabrera leandro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>jyzWX8yk</t>
+          <t>Ew10Xoy6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>herrera ander</t>
+          <t>llabres javier</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>t2Srcdis</t>
+          <t>CjwNDgqi</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>prados benat</t>
+          <t>muriqi vedat</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>OOFwBfsT</t>
+          <t>fToJY0qQ</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>marcao</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>hSbvVwW7</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>niguez saul</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hpZLKZVC</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>sancet ohian</t>
-        </is>
-      </c>
+          <t>van der heyden siebe</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Ao9Vw3hi</t>
+          <t>SChm1pCo</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>simon unai</t>
+          <t>exposito edu</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>OK0Lcg44</t>
+          <t>Cl8Ia7Q9</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>romero isaac</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>tUNr1qOE</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>sow djibril</t>
-        </is>
-      </c>
+          <t>puado javi</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>jmbMzvQa</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>carvalho william</t>
-        </is>
-      </c>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ULLmpdEb</t>
+          <t>ncU1c1uo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>isco</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>vFNb1rQ5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>sabaly youssouf</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>IsOwrMdM</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>cabrera leandro</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>SChm1pCo</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>exposito edu</t>
-        </is>
-      </c>
+          <t>munoz iker</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -746,152 +740,674 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>KApUeTtI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CMGUADgt</t>
+          <t>SjTBQO7b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>azpilicueta cesar</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>zPYmze7F</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ceballos dani</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>nm2Qvnyk</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>diaz brahim</t>
-        </is>
-      </c>
+          <t>park marvin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GW5JRBD0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>de la torre luca</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ITqxsbsR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jailson</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Wn6E2SED</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>mbappe kylian</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KxSmFSum</t>
+          <t>bygTWQzR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alfonso pedraza</t>
+          <t>anuar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>vcqiFPHQ</t>
+          <t>hGPnN7fG</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>foyth juan</t>
+          <t>chavarria pep</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S6QWzDng</t>
+          <t>vHFG4hw9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>kambwala willy</t>
+          <t>espino alfonso</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cz3awDFR</t>
+          <t>SdatvAiU</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>marmol mika</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>AerDGNDO</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>mckenna scott</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>UwfDD083</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>moreno gerard</t>
-        </is>
-      </c>
+          <t>mendez diego</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>8fnHDvMe</t>
+          <t>Iefc5Fwo</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>santos yeremi</t>
+          <t>ozkacar cenk</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SjTBQO7b</t>
+          <t>6NytetE5</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>park marvin</t>
+          <t>sanchez javier</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hKx3nCTp</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>alaba david</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KxSmFSum</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>alfonso pedraza</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>vcqiFPHQ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>foyth juan</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>S6QWzDng</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>kambwala willy</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>UwfDD083</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>moreno gerard</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>jVHfHxGn</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>perez ayoze</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>zPYmze7F</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ceballos dani</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>MVExOq3n</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>courtois thibaut</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>nm2Qvnyk</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>diaz brahim</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>xWwucZ71</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>suarez denis</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>vDI9I1M4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>artero ricard</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2iBBeOy8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>agirrezabala julen</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nev6Da3D</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>alvarez yeray</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ao9Vw3hi</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>simon unai</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>U5mPqlh6</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>blind daley</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>tGPWeqJs</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>WCC5IrWg</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>romeu oriol</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>8l99epoQ</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>tsygankov viktor</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>M3sbJix9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>araujo ronald</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>pf3IOiFD</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>bernal marc</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ShxiZhJI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>christensen andreas</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>xrV9v8CU</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>gavi</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2c2ipETG</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>marin fermin</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2oVBOlPg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>olmo dani</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>byxc46yl</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>ter stegen marc andre</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>hSbvVwW7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>niguez saul</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>jmbMzvQa</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>carvalho william</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ULLmpdEb</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>isco</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vFNb1rQ5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>sabaly youssouf</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>tUNr1qOE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>sow djibril</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fRSnvKQG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>traore hamari</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CMGUADgt</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>azpilicueta cesar</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8GVQFgH4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>le normand robin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>z3D5zvbD</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>llorente marcos</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>r7qw7OKg</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>zakharian arsen</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,104 +441,104 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_5</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_6</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_6</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_7</t>
@@ -547,79 +547,105 @@
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fwWfEJpk</t>
+          <t>vDI9I1M4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>garcia naim</t>
+          <t>artero ricard</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2gqO56Xu</t>
+          <t>U5mPqlh6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>diakhaby mouctar</t>
+          <t>blind daley</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KbobTIgr</t>
+          <t>tGPWeqJs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>domenech jaume</t>
+          <t>jastin antonino</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>xWguLPCU</t>
+          <t>WCC5IrWg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>gaya jose</t>
+          <t>romeu oriol</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IXRaCzVt</t>
+          <t>8l99epoQ</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>mir rafael</t>
+          <t>tsygankov viktor</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>M5U2cN2q</t>
+          <t>2iBBeOy8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>vazquez jesus</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+          <t>agirrezabala julen</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>nev6Da3D</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>alvarez yeray</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ao9Vw3hi</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>simon unai</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -628,102 +654,130 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IsOwrMdM</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>cabrera leandro</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ew10Xoy6</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>llabres javier</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CjwNDgqi</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>muriqi vedat</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>fToJY0qQ</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>van der heyden siebe</t>
-        </is>
-      </c>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>M3sbJix9</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>araujo ronald</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SChm1pCo</t>
+          <t>pf3IOiFD</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>exposito edu</t>
+          <t>bernal marc</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Cl8Ia7Q9</t>
+          <t>ShxiZhJI</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>puado javi</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+          <t>christensen andreas</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>xrV9v8CU</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>gavi</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2c2ipETG</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>marin fermin</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2oVBOlPg</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>olmo dani</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>6NtwHZ7F</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>szczesny wojciech</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>byxc46yl</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>ter stegen marc andre</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hSbvVwW7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>niguez saul</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ncU1c1uo</t>
+          <t>tUNr1qOE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>munoz iker</t>
+          <t>sow djibril</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -732,12 +786,36 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>jmbMzvQa</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>carvalho william</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ULLmpdEb</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>isco</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>vFNb1rQ5</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>sabaly youssouf</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -746,53 +824,71 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SjTBQO7b</t>
+          <t>fRSnvKQG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>park marvin</t>
+          <t>traore hamari</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GW5JRBD0</t>
+          <t>r7qw7OKg</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>de la torre luca</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ITqxsbsR</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>jailson</t>
-        </is>
-      </c>
+          <t>zakharian arsen</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CMGUADgt</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>azpilicueta cesar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>8GVQFgH4</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>le normand robin</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>z3D5zvbD</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>llorente marcos</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -801,77 +897,31 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>bygTWQzR</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>anuar</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>hGPnN7fG</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>chavarria pep</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>vHFG4hw9</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>espino alfonso</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SdatvAiU</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>mendez diego</t>
-        </is>
-      </c>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Iefc5Fwo</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>ozkacar cenk</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>6NytetE5</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>sanchez javier</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -880,360 +930,128 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>hKx3nCTp</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>alaba david</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>KxSmFSum</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>alfonso pedraza</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>vcqiFPHQ</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>foyth juan</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>S6QWzDng</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>kambwala willy</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>UwfDD083</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>moreno gerard</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>jVHfHxGn</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>perez ayoze</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>zPYmze7F</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>ceballos dani</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>MVExOq3n</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>courtois thibaut</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>nm2Qvnyk</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>diaz brahim</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>xWwucZ71</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>suarez denis</t>
-        </is>
-      </c>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>vDI9I1M4</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>artero ricard</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2iBBeOy8</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>agirrezabala julen</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>nev6Da3D</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>alvarez yeray</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Ao9Vw3hi</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>simon unai</t>
-        </is>
-      </c>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>U5mPqlh6</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>blind daley</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>tGPWeqJs</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>jastin antonino</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>WCC5IrWg</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>romeu oriol</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>8l99epoQ</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>tsygankov viktor</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>M3sbJix9</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>araujo ronald</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>pf3IOiFD</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>bernal marc</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ShxiZhJI</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>christensen andreas</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>xrV9v8CU</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>gavi</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2c2ipETG</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>marin fermin</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2oVBOlPg</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>olmo dani</t>
-        </is>
-      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>byxc46yl</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>ter stegen marc andre</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hSbvVwW7</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>niguez saul</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>jmbMzvQa</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>carvalho william</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ULLmpdEb</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>isco</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>vFNb1rQ5</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>sabaly youssouf</t>
-        </is>
-      </c>
+          <t>8Uo5ctIM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>tUNr1qOE</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>sow djibril</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1244,67 +1062,29 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>fRSnvKQG</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>traore hamari</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CMGUADgt</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>azpilicueta cesar</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>8GVQFgH4</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>le normand robin</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>z3D5zvbD</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>llorente marcos</t>
-        </is>
-      </c>
+          <t>0SQqjbAd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>r7qw7OKg</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>zakharian arsen</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1315,11 +1095,13 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1346,11 +1128,13 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1377,11 +1161,13 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1408,6 +1194,8 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Gz9WD123</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2g3Pa3qH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rosa lucas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +571,42 @@
           <t>YNHbsZ6C</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ChK2eOCj</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>paredes aitor</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ao9Vw3hi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>simon unai</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +614,66 @@
           <t>ll7vCuXF</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>jmbMzvQa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>carvalho william</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KxtC5I27</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>barja enrique</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ncU1c1uo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>munoz iker</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ULLmpdEb</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>isco</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dpUJtnsM</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>natan</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +681,90 @@
           <t>h2NyhKup</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6qVwC9AH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>elustondo aritz</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>vDI9I1M4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>artero ricard</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>U5mPqlh6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>blind daley</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>fRSnvKQG</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>traore hamari</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>r7qw7OKg</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>zakharian arsen</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>tGPWeqJs</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>n5xqpcKc</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>portu</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>WCC5IrWg</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>romeu oriol</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +772,98 @@
           <t>8Uo5ctIM</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hKx3nCTp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>alaba david</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>rVBGggAd</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>aspas iago</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GW5JRBD0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>de la torre luca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rZh5FTHE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>carvajal daniel</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MVExOq3n</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>courtois thibaut</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ITqxsbsR</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>jailson</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>MoAntFV8</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>kourouma moriba</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>nm2Qvnyk</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>diaz brahim</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CbwQ4Mws</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>vinicius junior</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +871,26 @@
           <t>0SQqjbAd</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +898,26 @@
           <t>65kl1OIc</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +925,26 @@
           <t>f1xuAJ1S</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +952,26 @@
           <t>2Xrca2mA</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +979,26 @@
           <t>QqTA4cPk</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -504,6 +1006,26 @@
           <t>vymauDyP</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -511,6 +1033,26 @@
           <t>x88gL4RQ</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -518,6 +1060,26 @@
           <t>dhkQFrkl</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -525,6 +1087,26 @@
           <t>8Sp1FEw8</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -532,6 +1114,26 @@
           <t>4zlpJdvq</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -539,6 +1141,26 @@
           <t>02sgHz9e</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -546,6 +1168,26 @@
           <t>naHJ2yf2</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -553,6 +1195,26 @@
           <t>842EOIGL</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -560,6 +1222,26 @@
           <t>jiAoNQdE</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -567,6 +1249,26 @@
           <t>E595Qvn9</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -471,62 +471,62 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
         </is>
       </c>
     </row>
@@ -624,26 +624,10 @@
           <t>carvalho william</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>KxtC5I27</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>barja enrique</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ncU1c1uo</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>munoz iker</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>ULLmpdEb</t>
@@ -654,16 +638,8 @@
           <t>isco</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dpUJtnsM</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>natan</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -683,12 +659,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6qVwC9AH</t>
+          <t>fRSnvKQG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>elustondo aritz</t>
+          <t>traore hamari</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -711,58 +687,58 @@
           <t>blind daley</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>fRSnvKQG</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>traore hamari</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>r7qw7OKg</t>
+          <t>tGPWeqJs</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>zakharian arsen</t>
+          <t>jastin antonino</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>tGPWeqJs</t>
+          <t>n5xqpcKc</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>jastin antonino</t>
+          <t>portu</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>n5xqpcKc</t>
+          <t>WCC5IrWg</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>portu</t>
+          <t>romeu oriol</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>WCC5IrWg</t>
+          <t>CxVKphX0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>romeu oriol</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>solis jhon</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>8l99epoQ</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>tsygankov viktor</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
     </row>
@@ -794,12 +770,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GW5JRBD0</t>
+          <t>ITqxsbsR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>de la torre luca</t>
+          <t>jailson</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -814,56 +790,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>MVExOq3n</t>
+          <t>MoAntFV8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>courtois thibaut</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>ITqxsbsR</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>jailson</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>MoAntFV8</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
           <t>kourouma moriba</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>nm2Qvnyk</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>diaz brahim</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CbwQ4Mws</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>vinicius junior</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -871,26 +815,82 @@
           <t>0SQqjbAd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hGPnN7fG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>chavarria pep</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>lrscbe6I</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>asano takuma</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ew10Xoy6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>llabres javier</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vHFG4hw9</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>espino alfonso</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CjwNDgqi</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>muriqi vedat</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>fToJY0qQ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>van der heyden siebe</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SdatvAiU</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>mendez diego</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,40 +425,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
@@ -471,89 +471,151 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_5</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_5</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_6</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_6</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_7</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_7</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_10</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2g3Pa3qH</t>
+          <t>lrscbe6I</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rosa lucas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>asano takuma</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ew10Xoy6</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>llabres javier</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>vHFG4hw9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>espino alfonso</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>hGPnN7fG</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>chavarria pep</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SdatvAiU</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>mendez diego</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -564,41 +626,63 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>65kl1OIc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CMGUADgt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>azpilicueta cesar</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ChK2eOCj</t>
+          <t>8GVQFgH4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>paredes aitor</t>
+          <t>le normand robin</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ao9Vw3hi</t>
+          <t>fwWfEJpk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>simon unai</t>
+          <t>garcia naim</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>z3D5zvbD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>llorente marcos</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -607,668 +691,311 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jmbMzvQa</t>
+          <t>KxSmFSum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>carvalho william</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>alfonso pedraza</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vcqiFPHQ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>foyth juan</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ULLmpdEb</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>isco</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>S6QWzDng</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>kambwala willy</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>UwfDD083</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>moreno gerard</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>jVHfHxGn</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>perez ayoze</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>xWwucZ71</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>suarez denis</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AkMslDtA</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>albiol raul</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>G8VcNrxU</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>bailly eric</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>EL0WleP6</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>costa logan</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>8fnHDvMe</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>santos yeremi</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fRSnvKQG</t>
+          <t>M3sbJix9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>traore hamari</t>
+          <t>araujo ronald</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>vDI9I1M4</t>
+          <t>pf3IOiFD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>artero ricard</t>
+          <t>bernal marc</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>U5mPqlh6</t>
+          <t>hSbvVwW7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>blind daley</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>niguez saul</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>zHxpGqc8</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>kouassi nianzou</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>tGPWeqJs</t>
+          <t>tUNr1qOE</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>jastin antonino</t>
+          <t>sow djibril</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>n5xqpcKc</t>
+          <t>ShxiZhJI</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>portu</t>
+          <t>christensen andreas</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>WCC5IrWg</t>
+          <t>byxc46yl</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>romeu oriol</t>
+          <t>ter stegen marc andre</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CxVKphX0</t>
+          <t>AVAVLaLt</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>solis jhon</t>
+          <t>torres ferran</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8l99epoQ</t>
+          <t>xrV9v8CU</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>tsygankov viktor</t>
+          <t>gavi</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hKx3nCTp</t>
+          <t>2gqO56Xu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alaba david</t>
+          <t>diakhaby mouctar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rVBGggAd</t>
+          <t>IXRaCzVt</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>aspas iago</t>
+          <t>mir rafael</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ITqxsbsR</t>
+          <t>SjTBQO7b</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>jailson</t>
+          <t>park marvin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>rZh5FTHE</t>
+          <t>fapXP9VS</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>carvajal daniel</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>MoAntFV8</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>kourouma moriba</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>ramirez sandro</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>M5U2cN2q</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>vazquez jesus</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>KbobTIgr</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>domenech jaume</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>0SQqjbAd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>hGPnN7fG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>chavarria pep</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>lrscbe6I</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>asano takuma</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ew10Xoy6</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>llabres javier</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>vHFG4hw9</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>espino alfonso</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>CjwNDgqi</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>muriqi vedat</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>fToJY0qQ</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>van der heyden siebe</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>SdatvAiU</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>mendez diego</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>65kl1OIc</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>f1xuAJ1S</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2Xrca2mA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>QqTA4cPk</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vymauDyP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>x88gL4RQ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dhkQFrkl</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8Sp1FEw8</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4zlpJdvq</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>02sgHz9e</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>naHJ2yf2</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>842EOIGL</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>jiAoNQdE</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>E595Qvn9</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,277 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_10</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_10</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_11</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_11</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>vymauDyP</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sj35PsHd</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>calero fernando</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SChm1pCo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>exposito edu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>QPoHzbRQ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>gragera jose</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>IcRlAoUb</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>unuvar naci</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8zvngfOe</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ejuke chidera</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hSbvVwW7</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>niguez saul</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Aexbrioc</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>suso</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +703,144 @@
           <t>x88gL4RQ</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0n8qUmN8</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>de la hoz cesar</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dEgxh8oM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>marcos andre</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Iefc5Fwo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ozkacar cenk</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>KxSmFSum</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>alfonso pedraza</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>vcqiFPHQ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>foyth juan</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>S6QWzDng</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>kambwala willy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>UwfDD083</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>moreno gerard</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>jVHfHxGn</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>perez ayoze</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>xWwucZ71</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>suarez denis</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>AkMslDtA</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>albiol raul</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>G8VcNrxU</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>bailly eric</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>EL0WleP6</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>costa logan</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>8fnHDvMe</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>santos yeremi</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +848,88 @@
           <t>dhkQFrkl</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>vHFG4hw9</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>espino alfonso</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SdatvAiU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mendez diego</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Gp35on1c</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>abqar abdelkebir</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>GfoivbEm</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>kike</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>KtWwVS3K</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>novoa ramos hugo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>h4BWTxSF</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>sedlar aleksandar</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +937,144 @@
           <t>8Sp1FEw8</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SjTBQO7b</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>park marvin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>fapXP9VS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ramirez sandro</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>vDI9I1M4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>artero ricard</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>xSXBYlvl</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gil bryan</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>tGPWeqJs</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rZes9CKA</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>lopez pau</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>n5xqpcKc</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>portu</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>WCC5IrWg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>romeu oriol</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>EauanyEm</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>ruiz abel</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>CxVKphX0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>solis jhon</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>8l99epoQ</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>tsygankov viktor</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>lnGG8RDp</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>asprilla yaser</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>U5mPqlh6</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>blind daley</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +1082,128 @@
           <t>4zlpJdvq</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hKx3nCTp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>alaba david</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>rZh5FTHE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>carvajal daniel</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MVExOq3n</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>courtois thibaut</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>nm2Qvnyk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>diaz brahim</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>M3sbJix9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>araujo ronald</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>pf3IOiFD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bernal marc</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ShxiZhJI</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>christensen andreas</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>byxc46yl</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ter stegen marc andre</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>AVAVLaLt</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>torres ferran</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AyxD3I5C</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>garcia eric</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>zPUyR5Up</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>rodrygo</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +1211,64 @@
           <t>02sgHz9e</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fwWfEJpk</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>garcia naim</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>GW5JRBD0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>de la torre luca</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ITqxsbsR</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>jailson</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1276,96 @@
           <t>naHJ2yf2</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8OTCRUh0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mayoral borja</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2gqO56Xu</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>diakhaby mouctar</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>IXRaCzVt</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>mir rafael</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>nosv3azp</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>pepelu</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>nosv3azp</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>pepelu</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>M5U2cN2q</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>vazquez jesus</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>KbobTIgr</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>domenech jaume</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1373,120 @@
           <t>842EOIGL</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>jmbMzvQa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>carvalho william</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ULLmpdEb</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>isco</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UZeyLfKI</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>lo celso giovani</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>dpUJtnsM</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>natan</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CMGUADgt</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>azpilicueta cesar</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AaZiGJ9E</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>barrios pablo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>8GVQFgH4</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>le normand robin</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rH0mL7ws</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>lenglet clement</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>z3D5zvbD</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>llorente marcos</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0SJZRycC</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>roca marc</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1494,104 @@
           <t>jiAoNQdE</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ye976xiA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>marin pablo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C8QkouJU</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>munoz aihen</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UmDjbtRC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>remiro alejandro</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>fRSnvKQG</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>traore hamari</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>KxtC5I27</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>barja enrique</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ncU1c1uo</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>munoz iker</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>r7qw7OKg</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>zakharian arsen</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>phTjGNq0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>zubeldia igor</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,76 +1599,40 @@
           <t>E595Qvn9</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>02cHDDPH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4z48FZf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dA00HeQh</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UaS8aGMt</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,277 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:AM9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_10</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_10</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_11</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_11</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_12</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_12</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_13</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_13</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>02cHDDPH</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KtWwVS3K</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>novoa ramos hugo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>lrscbe6I</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>asano takuma</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AXPRNqQn</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>costa samuel</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>lx119mnI</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cuellar ivan</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +703,44 @@
           <t>4z48FZf5</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,125 +748,709 @@
           <t>dA00HeQh</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>vDI9I1M4</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>artero ricard</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fwWfEJpk</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>garcia naim</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>pO8Jn4Xm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>dmitrovic marko</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EeUtTZld</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>garcia campos diego</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>lnGG8RDp</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>asprilla yaser</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>tYV4tvqr</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>groeneveld arnaut</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>OjpPzOu0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>frances alejandro</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>tGPWeqJs</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>vLPRaVJo</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>martin ivan</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>n5xqpcKc</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>portu</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>EauanyEm</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>ruiz abel</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>rZes9CKA</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>lopez pau</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2e75edda</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>misehouy gabriel osei</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>WCC5IrWg</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>romeu oriol</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>CxVKphX0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>solis jhon</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>8l99epoQ</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>tsygankov viktor</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Ie17FSsK</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>haller sebastien</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2cPwbh8J</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>raba daniel</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>EwStt8o4</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>saenz jorge</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CMGUADgt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>azpilicueta cesar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6qyeYCYO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>januzaj adnan</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SjTBQO7b</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>park marvin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>px36Cwpj</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>loiodice enzo</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8GVQFgH4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>le normand robin</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AaZiGJ9E</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>barrios pablo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>jX8PENMO</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>lemar thomas</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>z3D5zvbD</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>llorente marcos</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M3sbJix9</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>araujo ronald</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6o8Nnmm1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lozano pol</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sj35PsHd</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>calero fernando</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SChm1pCo</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>exposito edu</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>pf3IOiFD</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>bernal marc</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ShxiZhJI</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>christensen andreas</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>byxc46yl</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ter stegen marc andre</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>AVAVLaLt</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>torres ferran</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>AyxD3I5C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>garcia eric</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>QPoHzbRQ</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>gragera jose</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>YgxuEfvL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bade loic</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>fRSnvKQG</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>traore hamari</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ye976xiA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>marin pablo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>WtVfJtAm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>turrientes benat</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8zvngfOe</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ejuke chidera</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hSbvVwW7</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>niguez saul</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>UJ9btoDi</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>nyland orjan</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Aexbrioc</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>suso</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>zHxpGqc8</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>kouassi nianzou</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>GOkrxtHi</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>peque</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>r7qw7OKg</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>zakharian arsen</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ao9Vw3hi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>simon unai</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pxq49QlK</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>bellerin hector</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>jmbMzvQa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>carvalho william</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ULLmpdEb</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>isco</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>UZeyLfKI</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>lo celso giovani</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0SJZRycC</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>roca marc</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>jLOnYYdH</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>aitor rubal</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
           <t>zeCiJHet</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rPc4X7Gj</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nucZxUhT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bXuieB8c</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jFGHcfig</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>CMriQj9N</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Ia5ItCg4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UwPNKUWp</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MXB9rYOi</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QP8QvjOG</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
+++ b/data/spain/p6_deployment/data_understanding/df_match_player_next.xlsx
@@ -425,15 +425,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A11"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_9</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>rPc4X7Gj</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>vHFG4hw9</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>espino alfonso</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>dYFtDut6</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lopez unai</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>K2JPoFRo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>mumin abdul</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6qyeYCYO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>januzaj adnan</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>px36Cwpj</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>loiodice enzo</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>SjTBQO7b</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>park marvin</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +671,76 @@
           <t>nucZxUhT</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hKx3nCTp</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>alaba david</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>rZh5FTHE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>carvajal daniel</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>QkiZum3e</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>tchouameni aurelien</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>MVExOq3n</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>courtois thibaut</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>nscfER6B</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>valverde federico</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,55 +748,915 @@
           <t>bXuieB8c</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KxSmFSum</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>alfonso pedraza</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vcqiFPHQ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>foyth juan</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>UwfDD083</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>moreno gerard</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>K4275W3e</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>benavidez carlos</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>KtWwVS3K</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>novoa ramos hugo</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
-        </is>
-      </c>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SbettZSO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>neyou noupa yvan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EeUtTZld</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>garcia campos diego</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>fwWfEJpk</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>garcia naim</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>YgxuEfvL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>bade loic</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8zvngfOe</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ejuke chidera</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>zRYlzwwb</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>idumbo muzambo stanis</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Ie17FSsK</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>haller sebastien</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>AufokyHE</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>porozo jackson</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>EwStt8o4</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>saenz jorge</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>hSbvVwW7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>niguez saul</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>UJ9btoDi</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>nyland orjan</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aexbrioc</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>suso</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>zHxpGqc8</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>kouassi nianzou</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
-        </is>
-      </c>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>jmbMzvQa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>carvalho william</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ULLmpdEb</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>isco</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>jLOnYYdH</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>aitor rubal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ITqxsbsR</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>jailson</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>rHUdQZPd</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>carreira sergio</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>GW5JRBD0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>de la torre luca</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>UZeyLfKI</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>lo celso giovani</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>dpUJtnsM</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>natan</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0SJZRycC</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>roca marc</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
+          <t>Ia5ItCg4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lrscbe6I</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>asano takuma</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>lx119mnI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>cuellar ivan</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>nev0KWuA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>fernandez valery</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CMGUADgt</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>azpilicueta cesar</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8GVQFgH4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>le normand robin</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>jX8PENMO</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lemar thomas</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>CMriQj9N</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8YG04fHd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>berrocal juan</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>xnvqJMC1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>djene</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8OTCRUh0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>mayoral borja</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vDI9I1M4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>artero ricard</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>lnGG8RDp</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>asprilla yaser</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>tYV4tvqr</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>groeneveld arnaut</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2X8Yl4Ke</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ozgur bertug</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>OjpPzOu0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>frances alejandro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>tGPWeqJs</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>jastin antonino</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>n1iE7ch5</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>juan carlos</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2e75edda</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>misehouy gabriel osei</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>n5xqpcKc</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>portu</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>EauanyEm</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>ruiz abel</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
-        </is>
-      </c>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
-        </is>
-      </c>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fRSnvKQG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>traore hamari</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>zsQh7xdD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>aguerd naif</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>A3vo4Lf6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>barrenetxea muguruza ander</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>M3sbJix9</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>araujo ronald</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>pf3IOiFD</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>bernal marc</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ShxiZhJI</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>christensen andreas</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Ye976xiA</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>marin pablo</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>WtVfJtAm</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>turrientes benat</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>r7qw7OKg</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>zakharian arsen</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>AyxD3I5C</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>garcia eric</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>byxc46yl</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>ter stegen marc andre</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>AVAVLaLt</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>torres ferran</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>UgTrNwCF</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>cubarsi pau</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
-        </is>
-      </c>
+          <t>SCX7iT7M</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C2KEmK6l</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vVwOqx6D</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>buKPeYL5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IsCnpo0d</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
